--- a/research/traditional_assets/database/data/canada/canada_computers_peripherals.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_computers_peripherals.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,26 +587,23 @@
           <t>Computers/Peripherals</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.13</v>
-      </c>
       <c r="G2">
-        <v>-4.597861842105264</v>
+        <v>-3.886792452830189</v>
       </c>
       <c r="H2">
-        <v>-4.655427631578948</v>
+        <v>-3.886792452830189</v>
       </c>
       <c r="I2">
-        <v>-6.046052631578948</v>
+        <v>-3.528301886792453</v>
       </c>
       <c r="J2">
-        <v>-6.046052631578948</v>
+        <v>-3.528301886792453</v>
       </c>
       <c r="K2">
-        <v>-7.702999999999999</v>
+        <v>-4.37</v>
       </c>
       <c r="L2">
-        <v>-6.33470394736842</v>
+        <v>-4.122641509433962</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2.131</v>
+        <v>0.044</v>
       </c>
       <c r="V2">
-        <v>0.05365055387713998</v>
+        <v>0.002603550295857988</v>
       </c>
       <c r="W2">
-        <v>5.276243093922652</v>
+        <v>7.666666666666668</v>
       </c>
       <c r="X2">
-        <v>0.0800473015860703</v>
+        <v>0.1249182330251496</v>
       </c>
       <c r="Y2">
-        <v>5.196195792336582</v>
+        <v>7.541748433641518</v>
       </c>
       <c r="Z2">
-        <v>-3.514450867052024</v>
+        <v>0.3732394366197184</v>
       </c>
       <c r="AA2">
-        <v>0.8863109048723898</v>
+        <v>-1.316901408450704</v>
       </c>
       <c r="AB2">
-        <v>0.06737293132942156</v>
+        <v>0.1134427020794076</v>
       </c>
       <c r="AC2">
-        <v>0.8195968355427106</v>
+        <v>-1.430344110530112</v>
       </c>
       <c r="AD2">
-        <v>7.365</v>
+        <v>4.32</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>7.365</v>
+        <v>4.32</v>
       </c>
       <c r="AG2">
-        <v>5.234</v>
+        <v>4.276000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.1564192417967506</v>
+        <v>0.2035815268614515</v>
       </c>
       <c r="AI2">
-        <v>0.973176532769556</v>
+        <v>2.468571428571428</v>
       </c>
       <c r="AJ2">
-        <v>0.1164301285758776</v>
+        <v>0.201926709482433</v>
       </c>
       <c r="AK2">
-        <v>0.9626632334007724</v>
+        <v>2.506447831184055</v>
       </c>
       <c r="AL2">
-        <v>0.307</v>
+        <v>0.344</v>
       </c>
       <c r="AM2">
-        <v>0.305</v>
+        <v>0.344</v>
       </c>
       <c r="AN2">
-        <v>-1.022064945878435</v>
+        <v>-1.170731707317073</v>
       </c>
       <c r="AO2">
-        <v>-23.94788273615635</v>
+        <v>-10.87209302325581</v>
       </c>
       <c r="AP2">
-        <v>-0.7263391618096031</v>
+        <v>-1.158807588075881</v>
       </c>
       <c r="AQ2">
-        <v>-24.10491803278689</v>
+        <v>-10.87209302325581</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Skychain Technologies Inc. (TSXV:SCT)</t>
+          <t>Danavation Technologies Corp. (CNSX:DVN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-2.106529209621993</v>
+        <v>-3.886792452830189</v>
       </c>
       <c r="H3">
-        <v>-2.199312714776632</v>
+        <v>-3.886792452830189</v>
       </c>
       <c r="I3">
-        <v>-4.037800687285224</v>
+        <v>-3.528301886792453</v>
       </c>
       <c r="J3">
-        <v>-4.037800687285224</v>
+        <v>-3.528301886792453</v>
       </c>
       <c r="K3">
-        <v>-1.91</v>
+        <v>-4.37</v>
       </c>
       <c r="L3">
-        <v>-3.281786941580756</v>
+        <v>-4.122641509433962</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,326 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.875</v>
+        <v>0.044</v>
       </c>
       <c r="V3">
-        <v>0.1313813813813814</v>
+        <v>0.002603550295857988</v>
       </c>
       <c r="W3">
-        <v>5.276243093922652</v>
+        <v>7.666666666666668</v>
       </c>
       <c r="X3">
-        <v>0.08074004649243519</v>
+        <v>0.1249182330251496</v>
       </c>
       <c r="Y3">
-        <v>5.195503047430217</v>
+        <v>7.541748433641518</v>
       </c>
       <c r="Z3">
-        <v>-5.490566037735851</v>
+        <v>0.3732394366197184</v>
       </c>
       <c r="AA3">
-        <v>22.16981132075473</v>
+        <v>-1.316901408450704</v>
       </c>
       <c r="AB3">
-        <v>0.07055494614662314</v>
+        <v>0.1134427020794076</v>
       </c>
       <c r="AC3">
-        <v>22.09925637460811</v>
+        <v>-1.430344110530112</v>
       </c>
       <c r="AD3">
-        <v>2.14</v>
+        <v>4.32</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.14</v>
+        <v>4.32</v>
       </c>
       <c r="AG3">
-        <v>1.265</v>
+        <v>4.276000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.2431818181818182</v>
+        <v>0.2035815268614515</v>
       </c>
       <c r="AI3">
-        <v>0.5737265415549597</v>
+        <v>2.468571428571428</v>
       </c>
       <c r="AJ3">
-        <v>0.1596214511041009</v>
+        <v>0.201926709482433</v>
       </c>
       <c r="AK3">
-        <v>0.4430823117338003</v>
+        <v>2.506447831184055</v>
       </c>
       <c r="AL3">
-        <v>0.08799999999999999</v>
+        <v>0.344</v>
       </c>
       <c r="AM3">
-        <v>0.08599999999999999</v>
+        <v>0.344</v>
       </c>
       <c r="AN3">
-        <v>-0.9344978165938865</v>
+        <v>-1.170731707317073</v>
       </c>
       <c r="AO3">
-        <v>-26.70454545454546</v>
+        <v>-10.87209302325581</v>
       </c>
       <c r="AP3">
-        <v>-0.5524017467248908</v>
+        <v>-1.158807588075881</v>
       </c>
       <c r="AQ3">
-        <v>-27.32558139534884</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Tinkerine Studios Ltd. (TSXV:TTD)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Computers/Peripherals</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>-0.13</v>
-      </c>
-      <c r="G4">
-        <v>-1.221052631578947</v>
-      </c>
-      <c r="H4">
-        <v>-1.239473684210526</v>
-      </c>
-      <c r="I4">
-        <v>-1.005263157894737</v>
-      </c>
-      <c r="J4">
-        <v>-1.005263157894737</v>
-      </c>
-      <c r="K4">
-        <v>-0.373</v>
-      </c>
-      <c r="L4">
-        <v>-0.981578947368421</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0.036</v>
-      </c>
-      <c r="V4">
-        <v>0.01836734693877551</v>
-      </c>
-      <c r="W4">
-        <v>0.5920634920634921</v>
-      </c>
-      <c r="X4">
-        <v>0.0800473015860703</v>
-      </c>
-      <c r="Y4">
-        <v>0.5120161904774218</v>
-      </c>
-      <c r="Z4">
-        <v>-0.8816705336426914</v>
-      </c>
-      <c r="AA4">
-        <v>0.8863109048723898</v>
-      </c>
-      <c r="AB4">
-        <v>0.06671406932967924</v>
-      </c>
-      <c r="AC4">
-        <v>0.8195968355427106</v>
-      </c>
-      <c r="AD4">
-        <v>0.595</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0.595</v>
-      </c>
-      <c r="AG4">
-        <v>0.5589999999999999</v>
-      </c>
-      <c r="AH4">
-        <v>0.2328767123287671</v>
-      </c>
-      <c r="AI4">
-        <v>-2.680180180180181</v>
-      </c>
-      <c r="AJ4">
-        <v>0.221913457721318</v>
-      </c>
-      <c r="AK4">
-        <v>-2.166666666666667</v>
-      </c>
-      <c r="AL4">
-        <v>0.075</v>
-      </c>
-      <c r="AM4">
-        <v>0.075</v>
-      </c>
-      <c r="AN4">
-        <v>-1.46551724137931</v>
-      </c>
-      <c r="AO4">
-        <v>-5.093333333333334</v>
-      </c>
-      <c r="AP4">
-        <v>-1.376847290640394</v>
-      </c>
-      <c r="AQ4">
-        <v>-5.093333333333334</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Danavation Technologies Corp. (CNSX:DVN)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Computers/Peripherals</t>
-        </is>
-      </c>
-      <c r="G5">
-        <v>-15.35826771653543</v>
-      </c>
-      <c r="H5">
-        <v>-15.39370078740158</v>
-      </c>
-      <c r="I5">
-        <v>-18.18897637795276</v>
-      </c>
-      <c r="J5">
-        <v>-18.18897637795276</v>
-      </c>
-      <c r="K5">
-        <v>-5.42</v>
-      </c>
-      <c r="L5">
-        <v>-21.33858267716536</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>1.22</v>
-      </c>
-      <c r="V5">
-        <v>0.03922829581993569</v>
-      </c>
-      <c r="W5">
-        <v>11.10655737704918</v>
-      </c>
-      <c r="X5">
-        <v>0.07400977545167764</v>
-      </c>
-      <c r="Y5">
-        <v>11.0325476015975</v>
-      </c>
-      <c r="Z5">
-        <v>1.329842931937172</v>
-      </c>
-      <c r="AA5">
-        <v>-24.18848167539266</v>
-      </c>
-      <c r="AB5">
-        <v>0.06737293132942156</v>
-      </c>
-      <c r="AC5">
-        <v>-24.25585460672209</v>
-      </c>
-      <c r="AD5">
-        <v>4.63</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>4.63</v>
-      </c>
-      <c r="AG5">
-        <v>3.41</v>
-      </c>
-      <c r="AH5">
-        <v>0.1295829834872656</v>
-      </c>
-      <c r="AI5">
-        <v>1.140394088669951</v>
-      </c>
-      <c r="AJ5">
-        <v>0.09881193856853085</v>
-      </c>
-      <c r="AK5">
-        <v>1.200704225352113</v>
-      </c>
-      <c r="AL5">
-        <v>0.144</v>
-      </c>
-      <c r="AM5">
-        <v>0.144</v>
-      </c>
-      <c r="AN5">
-        <v>-1.026607538802661</v>
-      </c>
-      <c r="AO5">
-        <v>-32.08333333333334</v>
-      </c>
-      <c r="AP5">
-        <v>-0.7560975609756099</v>
-      </c>
-      <c r="AQ5">
-        <v>-32.08333333333334</v>
+        <v>-10.87209302325581</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/canada/canada_computers_peripherals.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_computers_peripherals.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-3.886792452830189</v>
+        <v>-1.814569536423841</v>
       </c>
       <c r="H2">
-        <v>-3.886792452830189</v>
+        <v>-1.814569536423841</v>
       </c>
       <c r="I2">
-        <v>-3.528301886792453</v>
+        <v>-1.635761589403974</v>
       </c>
       <c r="J2">
-        <v>-3.528301886792453</v>
+        <v>-1.635761589403974</v>
       </c>
       <c r="K2">
-        <v>-4.37</v>
+        <v>-3.03</v>
       </c>
       <c r="L2">
-        <v>-4.122641509433962</v>
+        <v>-2.006622516556291</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.044</v>
+        <v>0.029</v>
       </c>
       <c r="V2">
-        <v>0.002603550295857988</v>
+        <v>0.005282331511839709</v>
       </c>
       <c r="W2">
-        <v>7.666666666666668</v>
+        <v>1.178988326848249</v>
       </c>
       <c r="X2">
-        <v>0.1249182330251496</v>
+        <v>0.1315578441395233</v>
       </c>
       <c r="Y2">
-        <v>7.541748433641518</v>
+        <v>1.047430482708726</v>
       </c>
       <c r="Z2">
-        <v>0.3732394366197184</v>
+        <v>0.8851113716295426</v>
       </c>
       <c r="AA2">
-        <v>-1.316901408450704</v>
+        <v>-1.447831184056272</v>
       </c>
       <c r="AB2">
-        <v>0.1134427020794076</v>
+        <v>0.08946639700257258</v>
       </c>
       <c r="AC2">
-        <v>-1.430344110530112</v>
+        <v>-1.537297581058844</v>
       </c>
       <c r="AD2">
-        <v>4.32</v>
+        <v>4.61</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4.32</v>
+        <v>4.61</v>
       </c>
       <c r="AG2">
-        <v>4.276000000000001</v>
+        <v>4.581</v>
       </c>
       <c r="AH2">
-        <v>0.2035815268614515</v>
+        <v>0.4564356435643564</v>
       </c>
       <c r="AI2">
-        <v>2.468571428571428</v>
+        <v>24.26315789473679</v>
       </c>
       <c r="AJ2">
-        <v>0.201926709482433</v>
+        <v>0.4548704200178731</v>
       </c>
       <c r="AK2">
-        <v>2.506447831184055</v>
+        <v>28.45341614906824</v>
       </c>
       <c r="AL2">
-        <v>0.344</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AM2">
-        <v>0.344</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AN2">
-        <v>-1.170731707317073</v>
+        <v>-1.945147679324895</v>
       </c>
       <c r="AO2">
-        <v>-10.87209302325581</v>
+        <v>-4.418604651162791</v>
       </c>
       <c r="AP2">
-        <v>-1.158807588075881</v>
+        <v>-1.932911392405063</v>
       </c>
       <c r="AQ2">
-        <v>-10.87209302325581</v>
+        <v>-4.418604651162791</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-3.886792452830189</v>
+        <v>-1.814569536423841</v>
       </c>
       <c r="H3">
-        <v>-3.886792452830189</v>
+        <v>-1.814569536423841</v>
       </c>
       <c r="I3">
-        <v>-3.528301886792453</v>
+        <v>-1.635761589403974</v>
       </c>
       <c r="J3">
-        <v>-3.528301886792453</v>
+        <v>-1.635761589403974</v>
       </c>
       <c r="K3">
-        <v>-4.37</v>
+        <v>-3.03</v>
       </c>
       <c r="L3">
-        <v>-4.122641509433962</v>
+        <v>-2.006622516556291</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.044</v>
+        <v>0.029</v>
       </c>
       <c r="V3">
-        <v>0.002603550295857988</v>
+        <v>0.005282331511839709</v>
       </c>
       <c r="W3">
-        <v>7.666666666666668</v>
+        <v>1.178988326848249</v>
       </c>
       <c r="X3">
-        <v>0.1249182330251496</v>
+        <v>0.1315578441395233</v>
       </c>
       <c r="Y3">
-        <v>7.541748433641518</v>
+        <v>1.047430482708726</v>
       </c>
       <c r="Z3">
-        <v>0.3732394366197184</v>
+        <v>0.8851113716295426</v>
       </c>
       <c r="AA3">
-        <v>-1.316901408450704</v>
+        <v>-1.447831184056272</v>
       </c>
       <c r="AB3">
-        <v>0.1134427020794076</v>
+        <v>0.08946639700257258</v>
       </c>
       <c r="AC3">
-        <v>-1.430344110530112</v>
+        <v>-1.537297581058844</v>
       </c>
       <c r="AD3">
-        <v>4.32</v>
+        <v>4.61</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.32</v>
+        <v>4.61</v>
       </c>
       <c r="AG3">
-        <v>4.276000000000001</v>
+        <v>4.581</v>
       </c>
       <c r="AH3">
-        <v>0.2035815268614515</v>
+        <v>0.4564356435643564</v>
       </c>
       <c r="AI3">
-        <v>2.468571428571428</v>
+        <v>24.26315789473679</v>
       </c>
       <c r="AJ3">
-        <v>0.201926709482433</v>
+        <v>0.4548704200178731</v>
       </c>
       <c r="AK3">
-        <v>2.506447831184055</v>
+        <v>28.45341614906824</v>
       </c>
       <c r="AL3">
-        <v>0.344</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AM3">
-        <v>0.344</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AN3">
-        <v>-1.170731707317073</v>
+        <v>-1.945147679324895</v>
       </c>
       <c r="AO3">
-        <v>-10.87209302325581</v>
+        <v>-4.418604651162791</v>
       </c>
       <c r="AP3">
-        <v>-1.158807588075881</v>
+        <v>-1.932911392405063</v>
       </c>
       <c r="AQ3">
-        <v>-10.87209302325581</v>
+        <v>-4.418604651162791</v>
       </c>
     </row>
   </sheetData>
